--- a/public/downloads/event-budget-template.xlsx
+++ b/public/downloads/event-budget-template.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="68">
   <si>
     <t>Category</t>
   </si>
@@ -212,7 +212,10 @@
     <t>Totals are formulas — they update as you type. If you insert rows, extend the SUM range.</t>
   </si>
   <si>
-    <t>cuequote.com</t>
+    <t>The AV portion of this budget is the part that takes longest to estimate. Describe the event and CueQuote returns a costed equipment list you can paste straight into these rows, in about two minutes.</t>
+  </si>
+  <si>
+    <t>Start free at cuequote.com</t>
   </si>
 </sst>
 </file>
@@ -1228,7 +1231,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:A11"/>
+  <dimension ref="A1:A12"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="110" customWidth="1"/>
@@ -1289,6 +1292,11 @@
         <v>66</v>
       </c>
     </row>
+    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>67</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>

--- a/public/downloads/event-budget-template.xlsx
+++ b/public/downloads/event-budget-template.xlsx
@@ -212,7 +212,7 @@
     <t>Totals are formulas — they update as you type. If you insert rows, extend the SUM range.</t>
   </si>
   <si>
-    <t>The AV portion of this budget is the part that takes longest to estimate. Describe the event and CueQuote returns a costed equipment list you can paste straight into these rows, in about two minutes.</t>
+    <t>The AV portion of this budget is the part that takes longest to estimate. Describe the event and CueQuote returns a costed equipment list you can paste straight into these rows, in minutes.</t>
   </si>
   <si>
     <t>Start free at cuequote.com</t>
